--- a/data/trans_camb/IP19C05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,22</t>
+          <t>0,84; 7,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,9</t>
+          <t>1,13; 10,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,68</t>
+          <t>0,94; 5,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,15</t>
+          <t>1,15; 6,74</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,89</t>
+          <t>-2,79; 2,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,33</t>
+          <t>-1,14; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,46</t>
+          <t>0,44; 6,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,15</t>
+          <t>-1,89; 1,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,53</t>
+          <t>-0,37; 3,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,87</t>
+          <t>-0,88; 2,63</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,85; 879,65</t>
+          <t>-61,69; inf</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 862,92</t>
+          <t>-40,22; 759,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 749,34</t>
+          <t>-58,66; 538,96</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 9,44</t>
+          <t>0,27; 8,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,65</t>
+          <t>-1,81; 4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,0</t>
+          <t>-4,15; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,94</t>
+          <t>-1,67; 3,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,95</t>
+          <t>-0,44; 4,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,83</t>
+          <t>-1,24; 2,89</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,37; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,22</t>
+          <t>-0,92; 6,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,06</t>
+          <t>-1,17; 5,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -0,71</t>
+          <t>-6,39; -0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,91</t>
+          <t>-4,88; 2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,59</t>
+          <t>-2,72; 1,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,51</t>
+          <t>-2,06; 2,59</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 353,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 457,91</t>
+          <t>-80,61; 451,25</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,45</t>
+          <t>0,2; 3,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,32</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,12</t>
+          <t>-0,69; 2,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,15; 2,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,27</t>
+          <t>0,05; 2,28</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 902,71</t>
+          <t>-7,26; 948,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 836,63</t>
+          <t>-10,95; 904,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 522,94</t>
+          <t>-47,01; 524,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,87; 496,75</t>
+          <t>-52,76; 479,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,29; 421,86</t>
+          <t>0,5; 370,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,03; 411,11</t>
+          <t>-11,9; 346,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,74</t>
+          <t>0,84; 8,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,89</t>
+          <t>1,1; 9,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,55</t>
+          <t>0,93; 5,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,74</t>
+          <t>1,34; 7,14</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,84</t>
+          <t>-2,79; 2,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,45</t>
+          <t>-1,1; 6,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,38</t>
+          <t>0,49; 6,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,15</t>
+          <t>-1,87; 1,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,55</t>
+          <t>-0,56; 3,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,63</t>
+          <t>-0,82; 2,63</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,69; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 759,86</t>
+          <t>-49,09; 793,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 538,96</t>
+          <t>-56,1; 606,22</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 8,99</t>
+          <t>-0,25; 8,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,55</t>
+          <t>-1,85; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,0</t>
+          <t>-4,56; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,09</t>
+          <t>-1,67; 2,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,04</t>
+          <t>-0,56; 4,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,89</t>
+          <t>-1,23; 2,82</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-79,15; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,16</t>
+          <t>-1,0; 5,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,8</t>
+          <t>-1,13; 4,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,71</t>
+          <t>-6,5; -0,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,05</t>
+          <t>-4,81; 2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,64</t>
+          <t>-2,47; 1,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,59</t>
+          <t>-2,16; 2,49</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 451,25</t>
+          <t>-77,14; 533,49</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,51</t>
+          <t>0,31; 3,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,05; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,13</t>
+          <t>-0,55; 2,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,31</t>
+          <t>0,17; 2,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,28</t>
+          <t>0,1; 2,17</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 948,17</t>
+          <t>-12,08; 812,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 904,66</t>
+          <t>-22,92; 717,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 524,91</t>
+          <t>-51,66; 594,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 479,87</t>
+          <t>-52,98; 707,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,5; 370,74</t>
+          <t>1,89; 396,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 346,45</t>
+          <t>-7,59; 410,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1,84</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,94</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,84; 8,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>1,12; 9,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,13</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,85</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,37</t>
+          <t>0,94; 5,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,14</t>
+          <t>1,08; 6,15</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1,81</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,85</t>
+          <t>0,49; 6,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 6,01</t>
+          <t>-1,88; 1,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,35</t>
+          <t>-2,81; 2,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,15</t>
+          <t>-1,17; 5,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,49</t>
+          <t>-0,36; 3,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,63</t>
+          <t>-0,87; 2,87</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>468,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-7,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-0,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>105,91%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>468,61%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,85; 879,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 793,94</t>
+          <t>-40,5; 862,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 606,22</t>
+          <t>-56,45; 749,34</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,92</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 8,26</t>
+          <t>-4,1; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,5</t>
+          <t>-1,65; 3,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,0</t>
+          <t>0,34; 9,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,98</t>
+          <t>-1,81; 4,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,1</t>
+          <t>-0,57; 3,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,82</t>
+          <t>-1,3; 2,83</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>400,06%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>100,77%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,15; —</t>
+          <t>-79,37; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,45</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,78</t>
+          <t>-6,95; -0,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,98</t>
+          <t>-4,83; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; -0,72</t>
+          <t>-0,99; 6,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,05</t>
+          <t>-1,21; 5,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,85</t>
+          <t>-2,5; 1,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,49</t>
+          <t>-2,2; 2,51</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-43,49%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>191,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>166,74%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-43,49%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 353,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 533,49</t>
+          <t>-86,26; 457,91</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,55</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,54</t>
+          <t>-0,61; 2,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,53</t>
+          <t>-0,66; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,18</t>
+          <t>0,2; 3,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,36</t>
+          <t>0,14; 3,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,22</t>
+          <t>0,17; 2,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,17</t>
+          <t>0,09; 2,27</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>71,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>171,83%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>160,17%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 812,05</t>
+          <t>-54,01; 522,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 717,05</t>
+          <t>-54,87; 496,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 594,21</t>
+          <t>-5,47; 902,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 707,1</t>
+          <t>-15,93; 836,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,89; 396,99</t>
+          <t>5,29; 421,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 410,21</t>
+          <t>2,03; 411,11</t>
         </is>
       </c>
     </row>
